--- a/artfynd/A 26931-2026 artfynd.xlsx
+++ b/artfynd/A 26931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117958795</v>
+        <v>117971973</v>
       </c>
       <c r="B2" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklubba</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Calocera glossoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Pers.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nyborg, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570115</v>
+        <v>570078</v>
       </c>
       <c r="R2" t="n">
-        <v>6479099</v>
+        <v>6479176</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,90 +761,80 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Quercus</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122030002</v>
+        <v>128429089</v>
       </c>
       <c r="B3" t="n">
-        <v>9400</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105076</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nyborg, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570089</v>
+        <v>570058</v>
       </c>
       <c r="R3" t="n">
-        <v>6479092</v>
+        <v>6479038</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,12 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,51 +885,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122060520</v>
+        <v>128420365</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>1334</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gyllensopp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Aureoboletus gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,17 +937,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyborg, Ög</t>
+          <t>Nyborg 2, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570057</v>
+        <v>570011</v>
       </c>
       <c r="R4" t="n">
-        <v>6479062</v>
+        <v>6479065</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,17 +966,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Drothem</t>
+          <t>Västra Husby</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,100 +999,63 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Populus tremula</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122116827</v>
+        <v>128410482</v>
       </c>
       <c r="B5" t="n">
-        <v>58215</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>3739</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nyborg, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570106</v>
+        <v>570045</v>
       </c>
       <c r="R5" t="n">
-        <v>6479057</v>
+        <v>6479063</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,12 +1079,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,64 +1108,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128410482</v>
+        <v>122060520</v>
       </c>
       <c r="B6" t="n">
-        <v>86999</v>
+        <v>91893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3739</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nyborg, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570045</v>
+        <v>570057</v>
       </c>
       <c r="R6" t="n">
-        <v>6479063</v>
+        <v>6479062</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,27 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:50</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med tall.</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,63 +1208,109 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Populus tremula</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128429089</v>
+        <v>122030002</v>
       </c>
       <c r="B7" t="n">
-        <v>92280</v>
+        <v>9414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>105076</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nyborg, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570058</v>
+        <v>570089</v>
       </c>
       <c r="R7" t="n">
-        <v>6479038</v>
+        <v>6479092</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1332,22 +1337,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,21 +1351,956 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Suvi Bergström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117958795</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>570115</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6479099</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121926611</v>
+      </c>
+      <c r="B9" t="n">
+        <v>61491</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>570112</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6479097</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115390219</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570098</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6479141</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>116627474</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570110</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6479135</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121213864</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>570094</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6479155</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122116827</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>570106</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6479057</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128423551</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyborg 2, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>570011</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6479065</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västra Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121926420</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>570076</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6479120</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26931-2026 artfynd.xlsx
+++ b/artfynd/A 26931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2302,6 +2302,122 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134573390</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyborg, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>570051</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6479123</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Suvi Bergström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Suvi Bergström, Stefan Phalagorn Bergström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26931-2026 artfynd.xlsx
+++ b/artfynd/A 26931-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117971973</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128429089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128420365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410482</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122060520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122030002</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117958795</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1597,6 +1637,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121926611</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115390219</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1835,6 +1885,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116627474</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1950,6 +2005,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121213864</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2065,6 +2125,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122116827</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2186,6 +2251,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128423551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2301,6 +2371,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121926420</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2417,8 +2492,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134573390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>